--- a/bomix-app/backend/excel/template/matrix.xlsx
+++ b/bomix-app/backend/excel/template/matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Programming\BOMIX\bomix-app\backend\excel\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A273F58-DEB0-4BA9-A8AD-1B1A711EC2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2D0752-0637-46C8-AF77-0DE767387741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13440" yWindow="2412" windowWidth="22776" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2040" yWindow="2712" windowWidth="22152" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMD" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
   <si>
     <t>HONG FU JIN PRECISION INDUSTRY(WUHAN) CO.,LTD</t>
   </si>
@@ -126,10 +126,6 @@
   </si>
   <si>
     <t>AD2,AD3,AD4,AD5,AD6,AD7</t>
-  </si>
-  <si>
-    <t>V</t>
-    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Phase: {{.Phase}}</t>
@@ -334,7 +330,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -365,17 +361,29 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -716,81 +724,82 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="9.75" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="23.25" customWidth="1"/>
     <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" customWidth="1"/>
     <col min="11" max="18" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -804,17 +813,17 @@
     <row r="4" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -873,25 +882,25 @@
         <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>20</v>
@@ -917,36 +926,34 @@
       <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="8" t="e">
+      <c r="I6" s="15">
         <f t="shared" ref="I6:I7" si="0">G6*J6</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J6" s="8" t="e">
+        <v>0</v>
+      </c>
+      <c r="J6" s="15">
         <f t="shared" ref="J6:J7" si="1">IF(EXACT(K6,"V"),$K$5,0)+IF(EXACT(L6,"V"),$L$5,0)+IF(EXACT(M6,"V"),$M$5,0)+IF(EXACT(N6,"V"),$N$5,0)+IF(EXACT(O6,"V"),$O$5,0)+IF(EXACT(P6,"V"),$P$5,0)+IF(EXACT(Q6,"V"),$Q$5,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17"/>
+      <c r="L6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="15" t="s">
         <v>19</v>
       </c>
       <c r="R6" s="8" t="s">
@@ -973,36 +980,34 @@
       <c r="G7" s="7">
         <v>6</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="9" t="e">
+      <c r="I7" s="16">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J7" s="9" t="e">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16">
         <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q7" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="18"/>
+      <c r="L7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="16" t="s">
         <v>19</v>
       </c>
       <c r="R7" s="9" t="s">
@@ -1010,9 +1015,9 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/bomix-app/backend/excel/template/matrix.xlsx
+++ b/bomix-app/backend/excel/template/matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Programming\BOMIX\bomix-app\backend\excel\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2D0752-0637-46C8-AF77-0DE767387741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651C3F67-4FEC-46CE-9AAA-287937F25A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="2712" windowWidth="22152" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMD" sheetId="2" r:id="rId1"/>
@@ -125,9 +125,6 @@
     <t>VPORT0402L101V05</t>
   </si>
   <si>
-    <t>AD2,AD3,AD4,AD5,AD6,AD7</t>
-  </si>
-  <si>
     <t>Phase: {{.Phase}}</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -185,6 +182,10 @@
   </si>
   <si>
     <t>{{.ModelQtyG}}</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>AJ1,AU2</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -362,29 +363,29 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,85 +722,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="23.25" customWidth="1"/>
-    <col min="9" max="9" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" customWidth="1"/>
     <col min="11" max="18" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -810,20 +811,20 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -850,7 +851,7 @@
       </c>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -882,31 +883,31 @@
         <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>42</v>
       </c>
@@ -926,41 +927,41 @@
       <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="12">
         <f t="shared" ref="I6:I7" si="0">G6*J6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="12">
         <f t="shared" ref="J6:J7" si="1">IF(EXACT(K6,"V"),$K$5,0)+IF(EXACT(L6,"V"),$L$5,0)+IF(EXACT(M6,"V"),$M$5,0)+IF(EXACT(N6,"V"),$N$5,0)+IF(EXACT(O6,"V"),$O$5,0)+IF(EXACT(P6,"V"),$P$5,0)+IF(EXACT(Q6,"V"),$Q$5,0)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" s="15" t="s">
+      <c r="K6" s="14"/>
+      <c r="L6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="12" t="s">
         <v>19</v>
       </c>
       <c r="R6" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>43</v>
       </c>
@@ -980,41 +981,41 @@
       <c r="G7" s="7">
         <v>6</v>
       </c>
-      <c r="H7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="16">
+      <c r="H7" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q7" s="16" t="s">
+      <c r="K7" s="15"/>
+      <c r="L7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="13" t="s">
         <v>19</v>
       </c>
       <c r="R7" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
